--- a/artfynd/A 58676-2021 artfynd.xlsx
+++ b/artfynd/A 58676-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58676-2021 artfynd.xlsx
+++ b/artfynd/A 58676-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72871470</v>
+        <v>119136964</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrvreta, Upl</t>
+          <t>Väg 1181, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707417.9192445956</v>
+        <v>707408</v>
       </c>
       <c r="R2" t="n">
-        <v>6675919.169619112</v>
+        <v>6675901</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Agstam-Norlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Karin Agstam-Norlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -799,12 +779,7 @@
         <v>72871479</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707417.9192445956</v>
+        <v>707418</v>
       </c>
       <c r="R3" t="n">
-        <v>6675919.169619112</v>
+        <v>6675919</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,19 +844,9 @@
           <t>2018-06-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +875,314 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119136963</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Väg 1181, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>707375</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6675971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Singö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119136962</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väg 1181, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>707381</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6675992</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Singö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72871470</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrvreta, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>707418</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6675919</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Singö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-06-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 58676-2021 artfynd.xlsx
+++ b/artfynd/A 58676-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119136964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871479</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119136963</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119136962</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,8 +1212,20 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871470</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>